--- a/accountant-skill/data/Jan2026/fixed_assets_ledger.xlsx
+++ b/accountant-skill/data/Jan2026/fixed_assets_ledger.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Fixed Assets" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fixed Assets" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1610</v>
+        <v>15100</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1610</v>
+        <v>15100</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1620</v>
+        <v>15200</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>1620</v>
+        <v>15200</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1630</v>
+        <v>15300</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1630</v>
+        <v>15300</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1650</v>
+        <v>15300</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1650</v>
+        <v>15300</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
